--- a/data/trans_bre/IP1001-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 5,05</t>
+          <t>-4,72; 5,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 1,38</t>
+          <t>-6,56; 1,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 7,22</t>
+          <t>-3,62; 6,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,51</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 5,73</t>
+          <t>-3,32; 4,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 2,33</t>
+          <t>-6,13; 2,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 3,75</t>
+          <t>-2,69; 3,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 6,93</t>
+          <t>0,76; 7,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,33; 472,48</t>
+          <t>-73,72; 328,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-89,51; 122,16</t>
+          <t>-87,83; 195,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>-85,46; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,23</t>
+          <t>-3,48; 2,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 5,37</t>
+          <t>-3,73; 5,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 5,82</t>
+          <t>-2,01; 5,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,21; -4,0</t>
+          <t>-16,82; -3,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 5,61</t>
+          <t>-5,11; 5,17</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,37</t>
+          <t>-3,8; 5,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,01; 3,63</t>
+          <t>-8,44; 3,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-87,39; 480,21</t>
+          <t>-100,0; 490,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-76,03; 124,84</t>
+          <t>-81,32; 100,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 15,23</t>
+          <t>-4,33; 13,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 14,84</t>
+          <t>0,31; 15,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 7,02</t>
+          <t>-5,13; 7,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-60,62; —</t>
+          <t>-67,84; 863,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 6,35</t>
+          <t>-4,06; 6,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 0,0</t>
+          <t>-8,39; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,87</t>
+          <t>0,0; 10,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 3,83</t>
+          <t>-8,63; 3,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,14 +1195,14 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 239,7</t>
+          <t>-100,0; 253,77</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 3,27</t>
+          <t>-1,34; 3,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 2,43</t>
+          <t>-0,78; 2,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,45</t>
+          <t>-2,9; 1,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 1,89</t>
+          <t>-11,42; 1,96</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-79,42; 42,2</t>
+          <t>-76,85; 41,97</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 1,5</t>
+          <t>-3,99; 1,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -0,99</t>
+          <t>-6,44; -1,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -0,41</t>
+          <t>-5,1; -0,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,69</t>
+          <t>-3,71; 0,67</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-84,1; 116,8</t>
+          <t>-85,32; 140,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,66</t>
+          <t>-100,0; 54,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 1,71</t>
+          <t>-1,02; 1,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 0,57</t>
+          <t>-2,1; 0,48</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,03</t>
+          <t>-1,68; 0,93</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,15</t>
+          <t>-3,25; 0,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-33,0; 81,16</t>
+          <t>-30,4; 91,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-61,45; 30,22</t>
+          <t>-62,11; 28,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-50,94; 51,19</t>
+          <t>-50,03; 50,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-66,49; 12,66</t>
+          <t>-68,88; 15,22</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 5,06</t>
+          <t>-4,71; 4,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 1,31</t>
+          <t>-6,19; 1,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 6,84</t>
+          <t>-3,75; 6,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 5,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 4,7</t>
+          <t>-2,99; 5,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,13; 2,82</t>
+          <t>-6,77; 2,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 3,56</t>
+          <t>-2,75; 3,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,11</t>
+          <t>0,68; 6,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,72; 328,37</t>
+          <t>-73,84; 450,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,83; 195,93</t>
+          <t>-94,4; 133,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-85,46; —</t>
+          <t>-83,74; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 2,19</t>
+          <t>-4,21; 2,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 5,52</t>
+          <t>-3,8; 5,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 5,9</t>
+          <t>-1,06; 5,89</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,82; -3,9</t>
+          <t>-17,42; -3,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 5,17</t>
+          <t>-4,67; 5,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 5,03</t>
+          <t>-3,69; 5,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 3,67</t>
+          <t>-8,7; 3,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 490,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-98,81; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-81,32; 100,49</t>
+          <t>-80,23; 110,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 13,8</t>
+          <t>-2,95; 14,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,31; 15,33</t>
+          <t>0,22; 16,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 7,37</t>
+          <t>-5,09; 6,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-67,84; 863,59</t>
+          <t>-64,18; 932,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 6,37</t>
+          <t>-4,19; 6,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 0,0</t>
+          <t>-8,68; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,95</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,63; 3,57</t>
+          <t>-8,29; 3,93</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 253,77</t>
+          <t>-100,0; 368,63</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,39</t>
+          <t>-0,96; 3,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,9</t>
+          <t>-0,86; 2,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 1,52</t>
+          <t>-2,86; 1,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 1,96</t>
+          <t>-12,06; 1,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-76,85; 41,97</t>
+          <t>-77,53; 39,03</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,64</t>
+          <t>-3,84; 1,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,44; -1,3</t>
+          <t>-6,47; -1,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -0,35</t>
+          <t>-5,18; -0,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 0,67</t>
+          <t>-3,64; 0,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,32; 140,39</t>
+          <t>-86,87; 103,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 60,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 54,25</t>
+          <t>-100,0; 41,85</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,82</t>
+          <t>-1,05; 1,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 0,48</t>
+          <t>-2,0; 0,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,93</t>
+          <t>-1,66; 1,09</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 0,28</t>
+          <t>-3,23; 0,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-30,4; 91,15</t>
+          <t>-33,83; 88,36</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-62,11; 28,04</t>
+          <t>-59,97; 39,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-50,03; 50,12</t>
+          <t>-50,5; 63,33</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-68,88; 15,22</t>
+          <t>-69,98; 8,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP1001-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP1001-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>1,24</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 4,98</t>
+          <t>-3,91; 5,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 1,4</t>
+          <t>-6,1; 1,38</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 6,73</t>
+          <t>-3,84; 7,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,51</t>
+          <t>0,0; 6,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>3,83</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 5,41</t>
+          <t>-3,15; 5,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 2,21</t>
+          <t>-7,09; 2,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 3,82</t>
+          <t>-2,86; 3,75</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,99</t>
+          <t>1,29; 9,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,84; 450,88</t>
+          <t>-74,33; 472,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-94,4; 133,83</t>
+          <t>-89,51; 122,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,74; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-8,63</t>
+          <t>-7,95</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 2,2</t>
+          <t>-3,49; 2,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 5,42</t>
+          <t>-3,89; 5,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 5,89</t>
+          <t>-1,97; 5,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,42; -3,3</t>
+          <t>-15,69; -3,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -960,17 +960,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 5,36</t>
+          <t>-4,4; 5,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 5,18</t>
+          <t>-3,34; 5,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 3,38</t>
+          <t>-8,01; 3,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,39; 480,21</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-98,81; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-80,23; 110,11</t>
+          <t>-76,03; 124,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 14,88</t>
+          <t>-1,77; 15,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,22; 16,2</t>
+          <t>-0,48; 14,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 6,89</t>
+          <t>-5,01; 7,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-64,18; 932,85</t>
+          <t>-60,62; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-2,06</t>
+          <t>-2,31</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-41,05%</t>
+          <t>-44,05%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 6,52</t>
+          <t>-3,95; 6,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 0,0</t>
+          <t>-8,6; 0,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,8</t>
+          <t>0,0; 11,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 3,93</t>
+          <t>-8,67; 3,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 368,63</t>
+          <t>-100,0; 221,4</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-4,0</t>
+          <t>-2,94</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-40,13%</t>
+          <t>-31,53%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,4</t>
+          <t>-1,3; 3,27</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 2,9</t>
+          <t>-0,85; 2,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 1,61</t>
+          <t>-2,86; 1,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 1,95</t>
+          <t>-9,16; 3,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-77,53; 39,03</t>
+          <t>-72,49; 55,27</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-1,34</t>
+          <t>-1,33</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-70,11%</t>
+          <t>-68,13%</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 1,53</t>
+          <t>-3,71; 1,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-6,47; -1,3</t>
+          <t>-6,23; -0,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-5,18; -0,4</t>
+          <t>-5,1; -0,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 0,6</t>
+          <t>-3,76; 0,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,87; 103,96</t>
+          <t>-84,1; 116,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 60,22</t>
+          <t>-100,0; 42,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 41,85</t>
+          <t>-100,0; 27,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-1,04</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-40,57%</t>
+          <t>-31,01%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 1,84</t>
+          <t>-1,11; 1,71</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,64</t>
+          <t>-2,11; 0,57</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,09</t>
+          <t>-1,66; 1,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 0,16</t>
+          <t>-2,63; 0,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-33,83; 88,36</t>
+          <t>-33,0; 81,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-59,97; 39,68</t>
+          <t>-61,45; 30,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-50,5; 63,33</t>
+          <t>-50,94; 51,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-69,98; 8,57</t>
+          <t>-60,77; 28,34</t>
         </is>
       </c>
     </row>
